--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -32,7 +32,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/#terminologie-lahn</t>
+    <t>https://smt.esante.gouv.fr/#terminologie-lahn (use: secondary, )</t>
   </si>
   <si>
     <t>Version</t>
@@ -80,8 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>La liste des actes innovants hors nomenclature (LAHN), a été mise en place par la direction générale de l’offre de soins (DGOS) en 2024, dans le cadre du développement de l’innovation en santé,  en remplacement du dispositif RIHN plus liste complémentaire. La LAHN en est la fusion.  L’objectif est de soutenir l’innovation et de la dynamiser par une prise en charge et une évaluation rapide des actes innovant.
-La LAHN contient une liste d’actes innovants (biologie et anatomocytopathologie) pris en charge à titre transitoire moyennant un recueil de données pour leur évaluation.</t>
+    <t>La liste des actes innovants hors nomenclature (LAHN) a été mise en place par la direction générale de l’offre de soins (DGOS) en 2024, dans le cadre du développement de l’innovation en santé. Elle est la fusion du RIHN et de la Liste Complémentaire (LC). L’objectif est de soutenir l’innovation et de la dynamiser par une prise en charge et une évaluation rapide des actes innovants. La LAHN contient une liste d’actes innovants (biologie et anatomocytopathologie) pris en charge à titre transitoire moyennant un recueil de données pour leur évaluation.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T16:01:06+00:00</t>
+    <t>2025-11-26T08:37:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-26T08:37:36+00:00</t>
+    <t>2025-11-27T08:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T08:43:00+00:00</t>
+    <t>2025-11-28T09:15:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T09:15:19+00:00</t>
+    <t>2025-11-28T13:41:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-28T13:41:04+00:00</t>
+    <t>2025-12-08T15:29:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T15:29:34+00:00</t>
+    <t>2025-12-08T17:18:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-08T17:18:19+00:00</t>
+    <t>2025-12-10T13:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T13:53:18+00:00</t>
+    <t>2025-12-11T13:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-11T13:50:41+00:00</t>
+    <t>2025-12-15T15:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T15:13:27+00:00</t>
+    <t>2025-12-20T13:25:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-20T13:25:39+00:00</t>
+    <t>2026-01-07T09:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-07T09:16:12+00:00</t>
+    <t>2026-01-08T09:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-08T09:55:22+00:00</t>
+    <t>2026-01-15T10:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:39:04+00:00</t>
+    <t>2026-03-10T13:56:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T13:56:55+00:00</t>
+    <t>2026-03-13T11:12:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T11:12:59+00:00</t>
+    <t>2026-03-13T14:08:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:08:07+00:00</t>
+    <t>2026-03-16T09:36:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T09:36:58+00:00</t>
+    <t>2026-04-15T12:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:25:44+00:00</t>
+    <t>2026-04-21T11:09:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:09:45+00:00</t>
+    <t>2026-04-21T12:38:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T12:38:05+00:00</t>
+    <t>2026-04-21T14:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:44:55+00:00</t>
+    <t>2026-04-21T15:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T15:54:01+00:00</t>
+    <t>2026-04-22T10:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:26+00:00</t>
+    <t>2026-04-23T19:56:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T19:56:15+00:00</t>
+    <t>2026-04-24T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T09:23:28+00:00</t>
+    <t>2026-04-27T15:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-27T15:12:13+00:00</t>
+    <t>2026-05-12T11:56:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:56:23+00:00</t>
+    <t>2026-05-12T13:38:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T13:38:44+00:00</t>
+    <t>2026-05-12T15:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T15:57:24+00:00</t>
+    <t>2026-05-12T16:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:58:28+00:00</t>
+    <t>2026-05-12T20:14:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T20:14:18+00:00</t>
+    <t>2026-05-13T09:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T09:41:30+00:00</t>
+    <t>2026-05-13T10:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T10:55:41+00:00</t>
+    <t>2026-05-18T13:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T15:03:25+00:00</t>
+    <t>2026-06-21T11:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T11:24:04+00:00</t>
+    <t>2026-06-21T12:13:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T12:13:53+00:00</t>
+    <t>2026-06-21T13:26:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T13:26:08+00:00</t>
+    <t>2026-06-21T14:37:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T14:37:12+00:00</t>
+    <t>2026-06-21T15:36:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T15:36:29+00:00</t>
+    <t>2026-06-21T17:31:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T17:31:55+00:00</t>
+    <t>2026-06-21T18:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T18:39:37+00:00</t>
+    <t>2026-06-21T21:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-21T21:38:11+00:00</t>
+    <t>2026-06-22T02:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T02:12:35+00:00</t>
+    <t>2026-06-22T06:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T06:15:53+00:00</t>
+    <t>2026-06-22T09:45:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:45:10+00:00</t>
+    <t>2026-06-22T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T13:12:12+00:00</t>
+    <t>2026-06-22T20:46:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T20:46:27+00:00</t>
+    <t>2026-06-23T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T17:00:44+00:00</t>
+    <t>2026-06-24T07:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:19:56+00:00</t>
+    <t>2026-06-24T08:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:50:58+00:00</t>
+    <t>2026-06-24T10:14:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T10:14:00+00:00</t>
+    <t>2026-06-24T11:43:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T11:43:48+00:00</t>
+    <t>2026-06-24T13:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM_FINESS_New/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T13:47:07+00:00</t>
+    <t>2026-06-24T15:18:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
